--- a/PAPORI_재고입출고관리.xlsx
+++ b/PAPORI_재고입출고관리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enjoy\OneDrive\Documents\GitHub\papori-mall\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812C08BD-84ED-426B-88A4-9A0A857D6A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42558F3F-F482-45F2-8C9C-8A3CD57AB9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9DCCABE-11A7-4EEF-924B-6BDB2488544C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{F9DCCABE-11A7-4EEF-924B-6BDB2488544C}"/>
   </bookViews>
   <sheets>
     <sheet name="사용법" sheetId="1" r:id="rId1"/>
@@ -8846,7 +8846,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="str">
-        <f t="shared" ref="F2:F65" si="0">IF(AND(D4&lt;&gt;"",E4&lt;&gt;""),D4*E4,"")</f>
+        <f t="shared" ref="F4:F65" si="0">IF(AND(D4&lt;&gt;"",E4&lt;&gt;""),D4*E4,"")</f>
         <v/>
       </c>
       <c r="G4" s="4"/>
@@ -40436,7 +40436,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5" t="str">
-        <f t="shared" ref="G2:G65" si="0">IF(E4="","",N(G3)+IF(B4="입금",E4,-E4))</f>
+        <f t="shared" ref="G4:G65" si="0">IF(E4="","",N(G3)+IF(B4="입금",E4,-E4))</f>
         <v/>
       </c>
       <c r="H4" s="4"/>
